--- a/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
+++ b/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
+++ b/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
+++ b/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
+++ b/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
+++ b/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
+++ b/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4300" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4300" uniqueCount="412">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -648,6 +648,10 @@
   </si>
   <si>
     <t>Kan bestå av antingen en registrationRecord, en pregnancyCheckupRecord eller en postDeliveryRecord.</t>
+  </si>
+  <si>
+    <t>getmaternitymedicalhistory-body-choice:En och endast en av registrationRecord, pregnancyCheckupRecord och postDeliveryRecord ska anges {registrationRecord.combine(pregnancyCheckupRecord).combine(postDeliveryRecord).count() = 1}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>SEEHDSLMMaternityMedicalHistory.maternityMedicalRecord.maternityMedicalRecordBody.id</t>
@@ -6259,15 +6263,15 @@
         <v>72</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6364,10 +6368,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6466,10 +6470,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6570,10 +6574,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6599,10 +6603,10 @@
         <v>78</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6653,7 +6657,7 @@
         <v>72</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>73</v>
@@ -6670,10 +6674,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6770,10 +6774,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6872,10 +6876,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6976,10 +6980,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7002,13 +7006,13 @@
         <v>72</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7059,7 +7063,7 @@
         <v>72</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>73</v>
@@ -7076,10 +7080,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7102,13 +7106,13 @@
         <v>72</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7159,7 +7163,7 @@
         <v>72</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>73</v>
@@ -7176,10 +7180,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7202,13 +7206,13 @@
         <v>72</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7259,7 +7263,7 @@
         <v>72</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>73</v>
@@ -7276,10 +7280,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7302,13 +7306,13 @@
         <v>72</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7359,7 +7363,7 @@
         <v>72</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>73</v>
@@ -7376,10 +7380,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7402,13 +7406,13 @@
         <v>72</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7459,7 +7463,7 @@
         <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>73</v>
@@ -7476,10 +7480,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7502,13 +7506,13 @@
         <v>72</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7559,7 +7563,7 @@
         <v>72</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>73</v>
@@ -7576,10 +7580,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7602,13 +7606,13 @@
         <v>72</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7659,7 +7663,7 @@
         <v>72</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>73</v>
@@ -7676,10 +7680,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7702,13 +7706,13 @@
         <v>72</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7759,7 +7763,7 @@
         <v>72</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>73</v>
@@ -7776,10 +7780,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7802,13 +7806,13 @@
         <v>72</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7859,7 +7863,7 @@
         <v>72</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>73</v>
@@ -7876,10 +7880,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7902,13 +7906,13 @@
         <v>72</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7959,7 +7963,7 @@
         <v>72</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>73</v>
@@ -7976,10 +7980,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8005,10 +8009,10 @@
         <v>78</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8059,7 +8063,7 @@
         <v>72</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>73</v>
@@ -8076,10 +8080,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8176,10 +8180,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8278,10 +8282,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8382,10 +8386,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8408,13 +8412,13 @@
         <v>72</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8465,7 +8469,7 @@
         <v>72</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -8482,10 +8486,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8508,13 +8512,13 @@
         <v>72</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8565,7 +8569,7 @@
         <v>72</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -8582,10 +8586,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8608,13 +8612,13 @@
         <v>72</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8665,7 +8669,7 @@
         <v>72</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>73</v>
@@ -8682,10 +8686,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8711,10 +8715,10 @@
         <v>113</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8765,7 +8769,7 @@
         <v>72</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>73</v>
@@ -8782,10 +8786,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8811,10 +8815,10 @@
         <v>113</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8865,7 +8869,7 @@
         <v>72</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>73</v>
@@ -8882,10 +8886,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8908,13 +8912,13 @@
         <v>72</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8965,7 +8969,7 @@
         <v>72</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>73</v>
@@ -8982,10 +8986,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9008,13 +9012,13 @@
         <v>72</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9065,7 +9069,7 @@
         <v>72</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>73</v>
@@ -9082,10 +9086,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9108,13 +9112,13 @@
         <v>72</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9165,7 +9169,7 @@
         <v>72</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>73</v>
@@ -9182,10 +9186,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9211,10 +9215,10 @@
         <v>191</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9265,7 +9269,7 @@
         <v>72</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>73</v>
@@ -9282,10 +9286,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9311,10 +9315,10 @@
         <v>191</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9365,7 +9369,7 @@
         <v>72</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>73</v>
@@ -9382,10 +9386,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9411,10 +9415,10 @@
         <v>191</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9465,7 +9469,7 @@
         <v>72</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>73</v>
@@ -9482,10 +9486,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9511,10 +9515,10 @@
         <v>191</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9565,7 +9569,7 @@
         <v>72</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>73</v>
@@ -9582,10 +9586,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9611,10 +9615,10 @@
         <v>78</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9665,7 +9669,7 @@
         <v>72</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>73</v>
@@ -9682,10 +9686,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9782,10 +9786,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9884,10 +9888,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9988,10 +9992,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10017,10 +10021,10 @@
         <v>113</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10071,7 +10075,7 @@
         <v>72</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -10088,10 +10092,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10117,10 +10121,10 @@
         <v>113</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10171,7 +10175,7 @@
         <v>72</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>73</v>
@@ -10188,10 +10192,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10217,10 +10221,10 @@
         <v>191</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10271,7 +10275,7 @@
         <v>72</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>73</v>
@@ -10288,10 +10292,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10317,10 +10321,10 @@
         <v>78</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10371,7 +10375,7 @@
         <v>72</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>73</v>
@@ -10388,10 +10392,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10488,10 +10492,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10590,10 +10594,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10694,10 +10698,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10720,13 +10724,13 @@
         <v>72</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10777,7 +10781,7 @@
         <v>72</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>73</v>
@@ -10794,10 +10798,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10820,13 +10824,13 @@
         <v>72</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -10877,7 +10881,7 @@
         <v>72</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>73</v>
@@ -10894,10 +10898,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10920,13 +10924,13 @@
         <v>72</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -10977,7 +10981,7 @@
         <v>72</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>73</v>
@@ -10994,10 +10998,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11020,13 +11024,13 @@
         <v>72</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -11077,7 +11081,7 @@
         <v>72</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>73</v>
@@ -11094,10 +11098,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11120,13 +11124,13 @@
         <v>72</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11177,7 +11181,7 @@
         <v>72</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>73</v>
@@ -11194,10 +11198,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11220,13 +11224,13 @@
         <v>72</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -11277,7 +11281,7 @@
         <v>72</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>73</v>
@@ -11294,10 +11298,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11320,13 +11324,13 @@
         <v>72</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11377,7 +11381,7 @@
         <v>72</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>73</v>
@@ -11394,10 +11398,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11420,13 +11424,13 @@
         <v>72</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11477,7 +11481,7 @@
         <v>72</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>73</v>
@@ -11494,10 +11498,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11520,13 +11524,13 @@
         <v>72</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11577,7 +11581,7 @@
         <v>72</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>73</v>
@@ -11594,10 +11598,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11620,13 +11624,13 @@
         <v>72</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11677,7 +11681,7 @@
         <v>72</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>73</v>
@@ -11694,10 +11698,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11720,13 +11724,13 @@
         <v>72</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -11777,7 +11781,7 @@
         <v>72</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>73</v>
@@ -11794,10 +11798,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11820,13 +11824,13 @@
         <v>72</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11877,7 +11881,7 @@
         <v>72</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>73</v>
@@ -11894,10 +11898,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11923,10 +11927,10 @@
         <v>78</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -11977,7 +11981,7 @@
         <v>72</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>73</v>
@@ -11994,10 +11998,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12094,10 +12098,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12196,10 +12200,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12300,10 +12304,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12329,10 +12333,10 @@
         <v>113</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12383,7 +12387,7 @@
         <v>72</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>83</v>
@@ -12400,10 +12404,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12429,10 +12433,10 @@
         <v>113</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12483,7 +12487,7 @@
         <v>72</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>73</v>
@@ -12500,10 +12504,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12529,10 +12533,10 @@
         <v>78</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -12583,7 +12587,7 @@
         <v>72</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>73</v>
@@ -12600,10 +12604,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12700,10 +12704,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12802,10 +12806,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12906,10 +12910,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12935,10 +12939,10 @@
         <v>78</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -12989,7 +12993,7 @@
         <v>72</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>83</v>
@@ -13006,10 +13010,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13106,10 +13110,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13208,10 +13212,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13312,10 +13316,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13338,13 +13342,13 @@
         <v>72</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -13395,7 +13399,7 @@
         <v>72</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>73</v>
@@ -13412,10 +13416,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13438,13 +13442,13 @@
         <v>72</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -13495,7 +13499,7 @@
         <v>72</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>73</v>
@@ -13512,10 +13516,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13538,13 +13542,13 @@
         <v>72</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -13595,7 +13599,7 @@
         <v>72</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>73</v>
@@ -13612,10 +13616,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13638,13 +13642,13 @@
         <v>72</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -13695,7 +13699,7 @@
         <v>72</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>73</v>
@@ -13712,10 +13716,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13741,10 +13745,10 @@
         <v>191</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -13795,7 +13799,7 @@
         <v>72</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>73</v>
@@ -13812,10 +13816,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13841,10 +13845,10 @@
         <v>191</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -13895,7 +13899,7 @@
         <v>72</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>73</v>
@@ -13912,10 +13916,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -13941,10 +13945,10 @@
         <v>191</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -13995,7 +13999,7 @@
         <v>72</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>73</v>
@@ -14012,10 +14016,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14041,10 +14045,10 @@
         <v>191</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -14095,7 +14099,7 @@
         <v>72</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>73</v>
@@ -14112,10 +14116,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14141,10 +14145,10 @@
         <v>191</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -14195,7 +14199,7 @@
         <v>72</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>73</v>
@@ -14212,10 +14216,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14241,10 +14245,10 @@
         <v>113</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -14295,7 +14299,7 @@
         <v>72</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>73</v>
@@ -14312,10 +14316,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14341,10 +14345,10 @@
         <v>191</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14395,7 +14399,7 @@
         <v>72</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>73</v>
@@ -14412,10 +14416,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14441,10 +14445,10 @@
         <v>78</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14495,7 +14499,7 @@
         <v>72</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>83</v>
@@ -14512,10 +14516,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14612,10 +14616,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14714,10 +14718,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14818,10 +14822,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -14844,13 +14848,13 @@
         <v>72</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -14901,7 +14905,7 @@
         <v>72</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>83</v>
@@ -14918,10 +14922,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -14944,13 +14948,13 @@
         <v>72</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -15001,7 +15005,7 @@
         <v>72</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>73</v>
@@ -15018,10 +15022,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15044,13 +15048,13 @@
         <v>72</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -15101,7 +15105,7 @@
         <v>72</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>73</v>
@@ -15118,10 +15122,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15144,13 +15148,13 @@
         <v>72</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -15201,7 +15205,7 @@
         <v>72</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>73</v>
@@ -15218,10 +15222,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15244,13 +15248,13 @@
         <v>72</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -15301,7 +15305,7 @@
         <v>72</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>73</v>

--- a/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
+++ b/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
+++ b/StructureDefinition-SEEHDSLMMaternityMedicalHistory.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
